--- a/Urban-Follower.xlsx
+++ b/Urban-Follower.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alsrj\Desktop\학술\찐찐막\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alsrj\Desktop\학술\찐찐막\Claude\VISSIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D55F23-9378-49AD-BA34-9395F8560DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27254E79-8947-4B75-8AD5-DD6E989D03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{C3DA5B16-8C92-4C5F-B32D-914F1DED688A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{C3DA5B16-8C92-4C5F-B32D-914F1DED688A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="12">
   <si>
     <t>Signal Head</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -461,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB2FDF5-D5D5-4FA6-BB40-178A2A4DF327}">
-  <dimension ref="A1:D276"/>
+  <dimension ref="A1:D333"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -4328,6 +4329,1699 @@
         <v>1030804</v>
       </c>
     </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A277">
+        <v>20</v>
+      </c>
+      <c r="B277">
+        <v>2001</v>
+      </c>
+      <c r="C277" t="s">
+        <v>4</v>
+      </c>
+      <c r="D277">
+        <v>90030902</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A278">
+        <v>20</v>
+      </c>
+      <c r="B278">
+        <v>2001</v>
+      </c>
+      <c r="C278" t="s">
+        <v>5</v>
+      </c>
+      <c r="D278">
+        <v>90030903</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A279">
+        <v>20</v>
+      </c>
+      <c r="B279">
+        <v>2001</v>
+      </c>
+      <c r="C279" t="s">
+        <v>5</v>
+      </c>
+      <c r="D279">
+        <v>90030904</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A280">
+        <v>20</v>
+      </c>
+      <c r="B280">
+        <v>2001</v>
+      </c>
+      <c r="C280" t="s">
+        <v>2</v>
+      </c>
+      <c r="D280">
+        <v>90030905</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A281">
+        <v>20</v>
+      </c>
+      <c r="B281">
+        <v>2001</v>
+      </c>
+      <c r="C281" t="s">
+        <v>3</v>
+      </c>
+      <c r="D281">
+        <v>90030906</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A282">
+        <v>20</v>
+      </c>
+      <c r="B282">
+        <v>2001</v>
+      </c>
+      <c r="C282" t="s">
+        <v>7</v>
+      </c>
+      <c r="D282">
+        <v>90030907</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A283">
+        <v>20</v>
+      </c>
+      <c r="B283">
+        <v>2001</v>
+      </c>
+      <c r="C283" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283">
+        <v>90030908</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A284">
+        <v>20</v>
+      </c>
+      <c r="B284">
+        <v>2001</v>
+      </c>
+      <c r="C284" t="s">
+        <v>6</v>
+      </c>
+      <c r="D284">
+        <v>90030909</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A285">
+        <v>20</v>
+      </c>
+      <c r="B285">
+        <v>2001</v>
+      </c>
+      <c r="C285" t="s">
+        <v>8</v>
+      </c>
+      <c r="D285">
+        <v>90030910</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A286">
+        <v>20</v>
+      </c>
+      <c r="B286">
+        <v>2001</v>
+      </c>
+      <c r="C286" t="s">
+        <v>9</v>
+      </c>
+      <c r="D286">
+        <v>90030911</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A287">
+        <v>21</v>
+      </c>
+      <c r="B287">
+        <v>2002</v>
+      </c>
+      <c r="C287" t="s">
+        <v>8</v>
+      </c>
+      <c r="D287">
+        <v>90030912</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A288">
+        <f t="shared" ref="A288:A298" si="0">A287</f>
+        <v>21</v>
+      </c>
+      <c r="B288">
+        <v>2002</v>
+      </c>
+      <c r="C288" t="s">
+        <v>9</v>
+      </c>
+      <c r="D288">
+        <v>90030913</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A289">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B289">
+        <v>2002</v>
+      </c>
+      <c r="C289" t="s">
+        <v>9</v>
+      </c>
+      <c r="D289">
+        <v>90030914</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A290">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B290">
+        <v>2002</v>
+      </c>
+      <c r="C290" t="s">
+        <v>7</v>
+      </c>
+      <c r="D290">
+        <v>90030969</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A291">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B291">
+        <v>2002</v>
+      </c>
+      <c r="C291" t="s">
+        <v>6</v>
+      </c>
+      <c r="D291">
+        <v>90030970</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A292">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B292">
+        <v>2002</v>
+      </c>
+      <c r="C292" t="s">
+        <v>6</v>
+      </c>
+      <c r="D292">
+        <v>90030971</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A293">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B293">
+        <v>2002</v>
+      </c>
+      <c r="C293" t="s">
+        <v>2</v>
+      </c>
+      <c r="D293">
+        <v>90030973</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A294">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B294">
+        <v>2002</v>
+      </c>
+      <c r="C294" t="s">
+        <v>3</v>
+      </c>
+      <c r="D294">
+        <v>90030974</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A295">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B295">
+        <v>2002</v>
+      </c>
+      <c r="C295" t="s">
+        <v>3</v>
+      </c>
+      <c r="D295">
+        <v>90030975</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A296">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B296">
+        <v>2002</v>
+      </c>
+      <c r="C296" t="s">
+        <v>4</v>
+      </c>
+      <c r="D296">
+        <v>90030976</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A297">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B297">
+        <v>2002</v>
+      </c>
+      <c r="C297" t="s">
+        <v>5</v>
+      </c>
+      <c r="D297">
+        <v>90030977</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A298">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B298">
+        <v>2002</v>
+      </c>
+      <c r="C298" t="s">
+        <v>5</v>
+      </c>
+      <c r="D298">
+        <v>90030978</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A299">
+        <v>22</v>
+      </c>
+      <c r="B299">
+        <v>2003</v>
+      </c>
+      <c r="C299" t="s">
+        <v>8</v>
+      </c>
+      <c r="D299">
+        <v>90030926</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A300">
+        <f t="shared" ref="A300:A307" si="1">A299</f>
+        <v>22</v>
+      </c>
+      <c r="B300">
+        <v>2003</v>
+      </c>
+      <c r="C300" t="s">
+        <v>8</v>
+      </c>
+      <c r="D300">
+        <v>90030927</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A301">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B301">
+        <v>2003</v>
+      </c>
+      <c r="C301" t="s">
+        <v>4</v>
+      </c>
+      <c r="D301">
+        <v>90030928</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A302">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B302">
+        <v>2003</v>
+      </c>
+      <c r="C302" t="s">
+        <v>4</v>
+      </c>
+      <c r="D302">
+        <v>90030929</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A303">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B303">
+        <v>2003</v>
+      </c>
+      <c r="C303" t="s">
+        <v>5</v>
+      </c>
+      <c r="D303">
+        <v>90030930</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A304">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B304">
+        <v>2003</v>
+      </c>
+      <c r="C304" t="s">
+        <v>5</v>
+      </c>
+      <c r="D304">
+        <v>90030931</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A305">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B305">
+        <v>2003</v>
+      </c>
+      <c r="C305" t="s">
+        <v>6</v>
+      </c>
+      <c r="D305">
+        <v>90030932</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A306">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B306">
+        <v>2003</v>
+      </c>
+      <c r="C306" t="s">
+        <v>6</v>
+      </c>
+      <c r="D306">
+        <v>90030933</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A307">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B307">
+        <v>2003</v>
+      </c>
+      <c r="C307" t="s">
+        <v>6</v>
+      </c>
+      <c r="D307">
+        <v>90030934</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A308">
+        <v>23</v>
+      </c>
+      <c r="B308">
+        <v>2004</v>
+      </c>
+      <c r="C308" t="s">
+        <v>4</v>
+      </c>
+      <c r="D308">
+        <v>90030935</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A309">
+        <f t="shared" ref="A309:A319" si="2">A308</f>
+        <v>23</v>
+      </c>
+      <c r="B309">
+        <v>2004</v>
+      </c>
+      <c r="C309" t="s">
+        <v>5</v>
+      </c>
+      <c r="D309">
+        <v>90030936</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A310">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B310">
+        <v>2004</v>
+      </c>
+      <c r="C310" t="s">
+        <v>5</v>
+      </c>
+      <c r="D310">
+        <v>90030937</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A311">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B311">
+        <v>2004</v>
+      </c>
+      <c r="C311" t="s">
+        <v>2</v>
+      </c>
+      <c r="D311">
+        <v>90030939</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A312">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B312">
+        <v>2004</v>
+      </c>
+      <c r="C312" t="s">
+        <v>3</v>
+      </c>
+      <c r="D312">
+        <v>90030940</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A313">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B313">
+        <v>2004</v>
+      </c>
+      <c r="C313" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313">
+        <v>90030941</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A314">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B314">
+        <v>2004</v>
+      </c>
+      <c r="C314" t="s">
+        <v>7</v>
+      </c>
+      <c r="D314">
+        <v>90030943</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A315">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B315">
+        <v>2004</v>
+      </c>
+      <c r="C315" t="s">
+        <v>6</v>
+      </c>
+      <c r="D315">
+        <v>90030944</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A316">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B316">
+        <v>2004</v>
+      </c>
+      <c r="C316" t="s">
+        <v>6</v>
+      </c>
+      <c r="D316">
+        <v>90030945</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A317">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B317">
+        <v>2004</v>
+      </c>
+      <c r="C317" t="s">
+        <v>8</v>
+      </c>
+      <c r="D317">
+        <v>90030947</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A318">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B318">
+        <v>2004</v>
+      </c>
+      <c r="C318" t="s">
+        <v>9</v>
+      </c>
+      <c r="D318">
+        <v>90030948</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A319">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B319">
+        <v>2004</v>
+      </c>
+      <c r="C319" t="s">
+        <v>9</v>
+      </c>
+      <c r="D319">
+        <v>90030949</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A320">
+        <v>24</v>
+      </c>
+      <c r="B320">
+        <v>2005</v>
+      </c>
+      <c r="C320" t="s">
+        <v>4</v>
+      </c>
+      <c r="D320">
+        <v>90030951</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A321">
+        <f t="shared" ref="A321:A333" si="3">A320</f>
+        <v>24</v>
+      </c>
+      <c r="B321">
+        <v>2005</v>
+      </c>
+      <c r="C321" t="s">
+        <v>5</v>
+      </c>
+      <c r="D321">
+        <v>90030952</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A322">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B322">
+        <v>2005</v>
+      </c>
+      <c r="C322" t="s">
+        <v>5</v>
+      </c>
+      <c r="D322">
+        <v>90030953</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A323">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B323">
+        <v>2005</v>
+      </c>
+      <c r="C323" t="s">
+        <v>2</v>
+      </c>
+      <c r="D323">
+        <v>90030955</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A324">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B324">
+        <v>2005</v>
+      </c>
+      <c r="C324" t="s">
+        <v>3</v>
+      </c>
+      <c r="D324">
+        <v>90030956</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A325">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B325">
+        <v>2005</v>
+      </c>
+      <c r="C325" t="s">
+        <v>3</v>
+      </c>
+      <c r="D325">
+        <v>90030957</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A326">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B326">
+        <v>2005</v>
+      </c>
+      <c r="C326" t="s">
+        <v>3</v>
+      </c>
+      <c r="D326">
+        <v>90030958</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A327">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B327">
+        <v>2005</v>
+      </c>
+      <c r="C327" t="s">
+        <v>7</v>
+      </c>
+      <c r="D327">
+        <v>90030960</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A328">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B328">
+        <v>2005</v>
+      </c>
+      <c r="C328" t="s">
+        <v>6</v>
+      </c>
+      <c r="D328">
+        <v>90030961</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A329">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B329">
+        <v>2005</v>
+      </c>
+      <c r="C329" t="s">
+        <v>6</v>
+      </c>
+      <c r="D329">
+        <v>90030962</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A330">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B330">
+        <v>2005</v>
+      </c>
+      <c r="C330" t="s">
+        <v>6</v>
+      </c>
+      <c r="D330">
+        <v>90030963</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A331">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B331">
+        <v>2005</v>
+      </c>
+      <c r="C331" t="s">
+        <v>8</v>
+      </c>
+      <c r="D331">
+        <v>90030965</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A332">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B332">
+        <v>2005</v>
+      </c>
+      <c r="C332" t="s">
+        <v>9</v>
+      </c>
+      <c r="D332">
+        <v>90030966</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A333">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B333">
+        <v>2005</v>
+      </c>
+      <c r="C333" t="s">
+        <v>9</v>
+      </c>
+      <c r="D333">
+        <v>90030967</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A318B792-1481-4F17-B5BB-C5F71C34CFD5}">
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1">
+        <v>20</v>
+      </c>
+      <c r="B1">
+        <v>90030902</v>
+      </c>
+      <c r="C1">
+        <v>2001</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>90030903</v>
+      </c>
+      <c r="C2">
+        <v>2001</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>90030904</v>
+      </c>
+      <c r="C3">
+        <v>2001</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>90030905</v>
+      </c>
+      <c r="C4">
+        <v>2001</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>90030906</v>
+      </c>
+      <c r="C5">
+        <v>2001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>90030907</v>
+      </c>
+      <c r="C6">
+        <v>2001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>90030908</v>
+      </c>
+      <c r="C7">
+        <v>2001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>90030909</v>
+      </c>
+      <c r="C8">
+        <v>2001</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>90030910</v>
+      </c>
+      <c r="C9">
+        <v>2001</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>90030911</v>
+      </c>
+      <c r="C10">
+        <v>2001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>90030912</v>
+      </c>
+      <c r="C11">
+        <v>2002</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <f t="shared" ref="A12:A22" si="0">A11</f>
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>90030913</v>
+      </c>
+      <c r="C12">
+        <v>2002</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>90030914</v>
+      </c>
+      <c r="C13">
+        <v>2002</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>90030969</v>
+      </c>
+      <c r="C14">
+        <v>2002</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>90030970</v>
+      </c>
+      <c r="C15">
+        <v>2002</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>90030971</v>
+      </c>
+      <c r="C16">
+        <v>2002</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B17">
+        <v>90030973</v>
+      </c>
+      <c r="C17">
+        <v>2002</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>90030974</v>
+      </c>
+      <c r="C18">
+        <v>2002</v>
+      </c>
+      <c r="D18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>90030975</v>
+      </c>
+      <c r="C19">
+        <v>2002</v>
+      </c>
+      <c r="D19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>90030976</v>
+      </c>
+      <c r="C20">
+        <v>2002</v>
+      </c>
+      <c r="D20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>90030977</v>
+      </c>
+      <c r="C21">
+        <v>2002</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>90030978</v>
+      </c>
+      <c r="C22">
+        <v>2002</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>90030926</v>
+      </c>
+      <c r="C23">
+        <v>2003</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <f t="shared" ref="A24:A31" si="1">A23</f>
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>90030927</v>
+      </c>
+      <c r="C24">
+        <v>2003</v>
+      </c>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>90030928</v>
+      </c>
+      <c r="C25">
+        <v>2003</v>
+      </c>
+      <c r="D25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B26">
+        <v>90030929</v>
+      </c>
+      <c r="C26">
+        <v>2003</v>
+      </c>
+      <c r="D26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B27">
+        <v>90030930</v>
+      </c>
+      <c r="C27">
+        <v>2003</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B28">
+        <v>90030931</v>
+      </c>
+      <c r="C28">
+        <v>2003</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B29">
+        <v>90030932</v>
+      </c>
+      <c r="C29">
+        <v>2003</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B30">
+        <v>90030933</v>
+      </c>
+      <c r="C30">
+        <v>2003</v>
+      </c>
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B31">
+        <v>90030934</v>
+      </c>
+      <c r="C31">
+        <v>2003</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>23</v>
+      </c>
+      <c r="B32">
+        <v>90030935</v>
+      </c>
+      <c r="C32">
+        <v>2004</v>
+      </c>
+      <c r="D32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <f t="shared" ref="A33:A43" si="2">A32</f>
+        <v>23</v>
+      </c>
+      <c r="B33">
+        <v>90030936</v>
+      </c>
+      <c r="C33">
+        <v>2004</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B34">
+        <v>90030937</v>
+      </c>
+      <c r="C34">
+        <v>2004</v>
+      </c>
+      <c r="D34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B35">
+        <v>90030939</v>
+      </c>
+      <c r="C35">
+        <v>2004</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B36">
+        <v>90030940</v>
+      </c>
+      <c r="C36">
+        <v>2004</v>
+      </c>
+      <c r="D36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B37">
+        <v>90030941</v>
+      </c>
+      <c r="C37">
+        <v>2004</v>
+      </c>
+      <c r="D37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B38">
+        <v>90030943</v>
+      </c>
+      <c r="C38">
+        <v>2004</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B39">
+        <v>90030944</v>
+      </c>
+      <c r="C39">
+        <v>2004</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B40">
+        <v>90030945</v>
+      </c>
+      <c r="C40">
+        <v>2004</v>
+      </c>
+      <c r="D40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B41">
+        <v>90030947</v>
+      </c>
+      <c r="C41">
+        <v>2004</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B42">
+        <v>90030948</v>
+      </c>
+      <c r="C42">
+        <v>2004</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B43">
+        <v>90030949</v>
+      </c>
+      <c r="C43">
+        <v>2004</v>
+      </c>
+      <c r="D43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>24</v>
+      </c>
+      <c r="B44">
+        <v>90030951</v>
+      </c>
+      <c r="C44">
+        <v>2005</v>
+      </c>
+      <c r="D44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <f t="shared" ref="A45:A108" si="3">A44</f>
+        <v>24</v>
+      </c>
+      <c r="B45">
+        <v>90030952</v>
+      </c>
+      <c r="C45">
+        <v>2005</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B46">
+        <v>90030953</v>
+      </c>
+      <c r="C46">
+        <v>2005</v>
+      </c>
+      <c r="D46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B47">
+        <v>90030955</v>
+      </c>
+      <c r="C47">
+        <v>2005</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B48">
+        <v>90030956</v>
+      </c>
+      <c r="C48">
+        <v>2005</v>
+      </c>
+      <c r="D48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B49">
+        <v>90030957</v>
+      </c>
+      <c r="C49">
+        <v>2005</v>
+      </c>
+      <c r="D49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B50">
+        <v>90030958</v>
+      </c>
+      <c r="C50">
+        <v>2005</v>
+      </c>
+      <c r="D50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B51">
+        <v>90030960</v>
+      </c>
+      <c r="C51">
+        <v>2005</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B52">
+        <v>90030961</v>
+      </c>
+      <c r="C52">
+        <v>2005</v>
+      </c>
+      <c r="D52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B53">
+        <v>90030962</v>
+      </c>
+      <c r="C53">
+        <v>2005</v>
+      </c>
+      <c r="D53" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B54">
+        <v>90030963</v>
+      </c>
+      <c r="C54">
+        <v>2005</v>
+      </c>
+      <c r="D54" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B55">
+        <v>90030965</v>
+      </c>
+      <c r="C55">
+        <v>2005</v>
+      </c>
+      <c r="D55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B56">
+        <v>90030966</v>
+      </c>
+      <c r="C56">
+        <v>2005</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B57">
+        <v>90030967</v>
+      </c>
+      <c r="C57">
+        <v>2005</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
